--- a/Luban/Config/Datas/Levels/L20/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L20/EnemyList.xlsx
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>L20 W1/25; N=50; EHP=316.800000; normal:17x25,normal:18x25</t>
+          <t>L20 W1/25; N=50; EHP=819.848173; normal:17x25,normal:18x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>L20 W2/25; N=56; EHP=371.527834; normal:17x28,normal:18x28</t>
+          <t>L20 W2/25; N=56; EHP=961.478585; normal:17x28,normal:18x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>3864136,3864673,3864019,3864136,3864673,3864019,3864136,3864673,3864091,3864136,3864673,3864099,3864136,3864673,3864099,3864136,3864673,3864107,3864136,3864673,3864115,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864136,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144</t>
+          <t>3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864673,3864136,3864136,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864144,3864136,3864136,3864136,3864136,3864136,3864136,3864136</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>L20 W3/25; N=62; EHP=455.056589; air:2x2,air:11x1,air:12x2,air:13x1,air:14x1,normal:17x19,normal:18x19,swarm:84x17</t>
+          <t>L20 W3/25; N=62; EHP=1264.499848; normal:17x26,normal:18x19,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>3866136,3866673,3866019,3866136,3866673,3866019,3866136,3866673,3866091,3866136,3866673,3866091,3866136,3866673,3866099,3866136,3866673,3866107,3866136,3866673,3866107,3866136,3866673,3866115,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144</t>
+          <t>3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866673,3866136,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144,3866144</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>L20 W4/25; N=68; EHP=574.708147; air:2x2,air:11x2,air:12x1,air:13x2,air:14x1,normal:17x20,normal:18x21,swarm:84x19</t>
+          <t>L20 W4/25; N=68; EHP=1602.198988; normal:17x20,normal:18x29,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>3868136,3868673,3868019,3868668,3868136,3868673,3868091,3868668,3868136,3868673,3868091,3868668,3868136,3868673,3868099,3868868,3868136,3868673,3868099,3868868,3868136,3868673,3868107,3868868,3868136,3868673,3868107,3868868,3868136,3868673,3868115,3868988,3868136,3868673,3868115,3868988,3868136,3868673,3868988,3868136,3868673,3868988,3868136,3868673,3868136,3868673,3868136,3868673,3868136,3868673,3868136,3868673,3868136,3868673,3868144,3868673,3868144,3868673,3868144,3868673,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144</t>
+          <t>3868136,3868019,3868019,3868668,3868136,3868091,3868091,3868668,3868136,3868091,3868091,3868668,3868136,3868099,3868099,3868868,3868136,3868099,3868099,3868868,3868136,3868107,3868107,3868868,3868136,3868107,3868107,3868868,3868136,3868115,3868115,3868988,3868136,3868115,3868115,3868988,3868136,3868673,3868988,3868136,3868673,3868988,3868136,3868673,3868136,3868673,3868136,3868673,3868136,3868673,3868136,3868673,3868136,3868673,3868144,3868673,3868144,3868673,3868144,3868673,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144,3868144</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>L20 W5/25; N=74; EHP=1077.194410; air:2x1,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x17,normal:18x17,medium:83x3,swarm:84x20,medium:108x4,medium:123x4</t>
+          <t>L20 W5/25; N=74; EHP=2823.646373; air:2x2,air:11x4,air:12x4,air:13x4,air:14x4,medium:83x3,medium:108x4,medium:123x4,normal:17x17,normal:18x17,swarm:84x11 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>3870136,3870673,3870242,3870019,3870668,3870136,3870673,3870242,3870019,3870668,3870136,3870673,3870466,3870091,3870668,3870136,3870673,3870466,3870091,3870668,3870136,3870673,3870466,3870099,3870868,3870136,3870673,3870514,3870099,3870868,3870136,3870673,3870514,3870107,3870868,3870136,3870673,3870786,3870107,3870868,3870136,3870673,3870786,3870115,3870988,3870136,3870673,3870115,3870988,3870136,3870673,3870988,3870136,3870673,3870988,3870136,3870673,3870144,3870673,3870144,3870673,3870144,3870673,3870144,3870673,3870144,3870673,3870144,3870673,3870144,3870673,3870144,3870673,3870144,3870673,3870144,3870144,3870144,3870144,3870144</t>
+          <t>3870136,3870019,3870242,3870019,3870668,3870136,3870019,3870242,3870019,3870668,3870136,3870091,3870466,3870091,3870668,3870136,3870091,3870466,3870091,3870668,3870136,3870099,3870466,3870099,3870868,3870136,3870099,3870514,3870099,3870868,3870136,3870107,3870514,3870107,3870868,3870136,3870107,3870786,3870107,3870868,3870136,3870115,3870786,3870115,3870988,3870136,3870115,3870115,3870988,3870136,3870673,3870988,3870136,3870673,3870988,3870136,3870673,3870144,3870673,3870144,3870673,3870144,3870673,3870144,3870673,3870144,3870673,3870144,3870673,3870144,3870673,3870144,3870673,3870144,3870673,3870144,3870144,3870144,3870144,3870144</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>L20 W6/25; N=80; EHP=1099.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x13,normal:18x14,fast:30x2,fast:58x3,fast:64x2,medium:83x4,swarm:84x22,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L20 W6/25; N=80; EHP=2882.619087; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x2,fast:58x3,fast:64x2,fast:98x2,medium:83x4,medium:108x4,medium:123x4,normal:17x13,normal:18x14,swarm:84x12 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>3872136,3872673,3872242,3872019,3872668,3872136,3872673,3872242,3872019,3872668,3872136,3872673,3872242,3872091,3872668,3872136,3872673,3872466,3872091,3872668,3872136,3872673,3872466,3872099,3872868,3872136,3872673,3872514,3872099,3872868,3872136,3872673,3872514,3872107,3872868,3872136,3872673,3872514,3872107,3872868,3872136,3872673,3872786,3872115,3872988,3872136,3872673,3872786,3872115,3872988,3872136,3872673,3872988,3872136,3872673,3872988,3872136,3872673,3872136,3872673,3872136,3872673,3872144,3872673,3872144,3872673,3872144,3872673,3872144,3872673,3872144,3872673,3872144,3872673,3872144,3872673,3872144,3872673,3872144,3872673,3872144,3872144,3872144,3872144,3872144,3872144</t>
+          <t>3872136,3872019,3872242,3872019,3872668,3872136,3872019,3872242,3872019,3872668,3872136,3872091,3872242,3872091,3872668,3872136,3872091,3872466,3872091,3872668,3872136,3872099,3872466,3872099,3872868,3872136,3872099,3872514,3872099,3872868,3872136,3872107,3872514,3872107,3872868,3872136,3872107,3872514,3872107,3872868,3872136,3872115,3872786,3872115,3872988,3872136,3872115,3872786,3872115,3872988,3872136,3872673,3872988,3872136,3872673,3872988,3872136,3872673,3872136,3872673,3872136,3872673,3872144,3872673,3872144,3872673,3872144,3872673,3872144,3872673,3872144,3872673,3872144,3872673,3872144,3872673,3872144,3872673,3872144,3872673,3872144,3872144,3872144,3872144,3872144,3872144</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>L20 W7/25; N=86; EHP=1233.000000; air:2x2,air:11x2,air:12x2,air:13x2,air:14x2,normal:17x15,normal:18x15,fast:30x3,fast:58x2,fast:64x3,medium:83x4,swarm:84x24,fast:98x2,medium:108x4,medium:123x4</t>
+          <t>L20 W7/25; N=86; EHP=3231.277323; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,fast:30x3,fast:58x2,fast:64x3,fast:98x2,medium:83x4,medium:108x4,medium:123x4,normal:17x15,normal:18x15,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>3874136,3874673,3874242,3874019,3874668,3874136,3874673,3874242,3874019,3874668,3874136,3874673,3874242,3874091,3874668,3874136,3874673,3874466,3874091,3874668,3874136,3874673,3874466,3874099,3874868,3874136,3874673,3874466,3874099,3874868,3874136,3874673,3874514,3874099,3874868,3874136,3874673,3874514,3874107,3874868,3874136,3874673,3874786,3874107,3874988,3874136,3874673,3874786,3874115,3874988,3874136,3874673,3874786,3874115,3874988,3874136,3874673,3874988,3874136,3874673,3874988,3874136,3874673,3874136,3874673,3874136,3874673,3874144,3874673,3874144,3874673,3874144,3874673,3874144,3874673,3874144,3874673,3874144,3874673,3874144,3874673,3874144,3874673,3874144,3874673,3874144,3874144,3874144,3874144,3874144,3874144,3874144</t>
+          <t>3874136,3874019,3874242,3874019,3874668,3874136,3874019,3874242,3874019,3874668,3874136,3874091,3874242,3874091,3874668,3874136,3874091,3874466,3874091,3874668,3874136,3874099,3874466,3874099,3874868,3874136,3874099,3874466,3874099,3874868,3874136,3874099,3874514,3874099,3874868,3874136,3874107,3874514,3874107,3874868,3874136,3874107,3874786,3874107,3874988,3874136,3874115,3874786,3874115,3874988,3874136,3874115,3874786,3874115,3874988,3874136,3874673,3874988,3874136,3874673,3874988,3874136,3874673,3874136,3874673,3874136,3874673,3874144,3874673,3874144,3874673,3874144,3874673,3874144,3874673,3874144,3874673,3874144,3874673,3874144,3874673,3874144,3874673,3874144,3874673,3874144,3874144,3874144,3874144,3874144,3874144,3874144</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>L20 W8/25; N=92; EHP=1585.000000; air:2x2,air:11x2,air:12x3,air:13x2,air:14x2,normal:17x16,normal:18x16,fast:30x3,fast:58x3,fast:64x2,medium:83x4,swarm:84x25,fast:98x3,medium:108x4,medium:123x5</t>
+          <t>L20 W8/25; N=92; EHP=4155.130740; air:2x4,air:11x4,air:12x6,air:13x4,air:14x4,fast:30x3,fast:58x3,fast:64x2,fast:98x3,medium:83x4,medium:108x4,medium:123x5,normal:17x16,normal:18x16,swarm:84x14 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>3876136,3876673,3876242,3876019,3876668,3876136,3876673,3876242,3876019,3876668,3876136,3876673,3876466,3876019,3876668,3876136,3876673,3876466,3876091,3876668,3876136,3876673,3876466,3876091,3876668,3876136,3876673,3876514,3876099,3876868,3876136,3876673,3876514,3876099,3876868,3876136,3876673,3876514,3876107,3876868,3876136,3876673,3876786,3876107,3876868,3876136,3876673,3876786,3876107,3876868,3876136,3876673,3876786,3876115,3876988,3876136,3876673,3876115,3876988,3876136,3876673,3876988,3876136,3876673,3876988,3876136,3876673,3876136,3876673,3876136,3876673,3876144,3876673,3876144,3876673,3876144,3876673,3876144,3876673,3876144,3876673,3876144,3876673,3876144,3876673,3876144,3876673,3876144,3876673,3876144,3876673,3876144,3876144,3876144,3876144,3876144,3876144,3876144</t>
+          <t>3876136,3876019,3876242,3876019,3876668,3876136,3876019,3876242,3876019,3876668,3876136,3876019,3876466,3876019,3876668,3876136,3876091,3876466,3876091,3876668,3876136,3876091,3876466,3876091,3876668,3876136,3876099,3876514,3876099,3876868,3876136,3876099,3876514,3876099,3876868,3876136,3876107,3876514,3876107,3876868,3876136,3876107,3876786,3876107,3876868,3876136,3876107,3876786,3876107,3876868,3876136,3876115,3876786,3876115,3876988,3876136,3876115,3876115,3876988,3876136,3876673,3876988,3876136,3876673,3876988,3876136,3876673,3876136,3876673,3876136,3876673,3876144,3876673,3876144,3876673,3876144,3876673,3876144,3876673,3876144,3876673,3876144,3876673,3876144,3876673,3876144,3876673,3876144,3876673,3876144,3876673,3876144,3876144,3876144,3876144,3876144,3876144,3876144</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>L20 W9/25; N=98; EHP=2022.000000; air:2x3,air:11x2,air:12x2,air:13x3,air:14x2,normal:17x17,normal:18x17,fast:30x2,fast:58x3,fast:64x3,medium:83x5,swarm:84x27,fast:98x3,medium:108x5,medium:123x4</t>
+          <t>L20 W9/25; N=98; EHP=5302.435548; air:2x6,air:11x4,air:12x4,air:13x6,air:14x4,fast:30x2,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x4,normal:17x17,normal:18x17,swarm:84x15 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>3878136,3878673,3878242,3878019,3878668,3878136,3878673,3878242,3878019,3878668,3878136,3878673,3878242,3878091,3878668,3878136,3878673,3878466,3878091,3878668,3878136,3878673,3878466,3878091,3878668,3878136,3878673,3878466,3878099,3878868,3878136,3878673,3878514,3878099,3878868,3878136,3878673,3878514,3878107,3878868,3878136,3878673,3878514,3878107,3878868,3878136,3878673,3878786,3878107,3878868,3878136,3878673,3878786,3878115,3878988,3878136,3878673,3878786,3878115,3878988,3878136,3878673,3878988,3878136,3878673,3878988,3878136,3878673,3878988,3878136,3878673,3878136,3878673,3878136,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878144,3878144,3878144,3878144,3878144,3878144</t>
+          <t>3878136,3878019,3878242,3878019,3878668,3878136,3878019,3878242,3878019,3878668,3878136,3878091,3878242,3878091,3878668,3878136,3878091,3878466,3878091,3878668,3878136,3878091,3878466,3878091,3878668,3878136,3878099,3878466,3878099,3878868,3878136,3878099,3878514,3878099,3878868,3878136,3878107,3878514,3878107,3878868,3878136,3878107,3878514,3878107,3878868,3878136,3878107,3878786,3878107,3878868,3878136,3878115,3878786,3878115,3878988,3878136,3878115,3878786,3878115,3878988,3878136,3878673,3878988,3878136,3878673,3878988,3878136,3878673,3878988,3878136,3878673,3878136,3878673,3878136,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878673,3878144,3878144,3878144,3878144,3878144,3878144,3878144</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>L20 W10/25; N=104; EHP=3728.000000; air:2x2,air:11x3,air:12x2,air:13x3,air:14x2,normal:17x18,normal:18x18,fast:30x3,fast:58x3,fast:64x3,medium:83x5,swarm:84x29,fast:98x3,medium:108x5,medium:123x5</t>
+          <t>L20 W10/25; N=104; EHP=9768.367500; air:2x4,air:11x6,air:12x4,air:13x6,air:14x4,fast:30x3,fast:58x3,fast:64x3,fast:98x3,medium:83x5,medium:108x5,medium:123x5,normal:17x18,normal:18x18,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>3880136,3880673,3880242,3880019,3880668,3880253,3880136,3880673,3880242,3880019,3880668,3880325,3880136,3880673,3880242,3880091,3880668,3880541,3880136,3880673,3880466,3880091,3880668,3880541,3880136,3880673,3880466,3880091,3880668,3880565,3880136,3880673,3880466,3880099,3880868,3880645,3880136,3880673,3880514,3880099,3880868,3880645,3880136,3880673,3880514,3880099,3880868,3880693,3880136,3880673,3880514,3880107,3880868,3880709,3880136,3880673,3880514,3880107,3880868,3880709,3880136,3880673,3880786,3880115,3880988,3881021,3880136,3880673,3880786,3880115,3880988,3880136,3880673,3880786,3880115,3880988,3880136,3880673,3880988,3880144,3880673,3880988,3880144,3880673,3880988,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880673,3880673,3880673</t>
+          <t>3880136,3880019,3880242,3880019,3880668,3880253,3880136,3880019,3880242,3880019,3880668,3880325,3880136,3880091,3880242,3880091,3880668,3880541,3880136,3880091,3880466,3880091,3880668,3880541,3880136,3880091,3880466,3880091,3880668,3880565,3880136,3880099,3880466,3880099,3880868,3880645,3880136,3880099,3880514,3880099,3880868,3880645,3880136,3880099,3880514,3880099,3880868,3880693,3880136,3880107,3880514,3880107,3880868,3880709,3880136,3880107,3880514,3880107,3880868,3880709,3880136,3880115,3880786,3880115,3880988,3881021,3880136,3880115,3880786,3880115,3880988,3880136,3880115,3880786,3880115,3880988,3880136,3880673,3880988,3880144,3880673,3880988,3880144,3880673,3880988,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880144,3880673,3880673,3880673,3880673</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>L20 W11/25; N=110; EHP=3803.000000; air:2x2,air:11x3,air:12x3,air:13x2,air:14x3,normal:17x14,normal:18x13,fast:30x3,heavy:31x1,heavy:40x1,fast:58x3,fast:64x4,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x5,swarm:84x30,heavy:86x1,heavy:88x2,fast:98x3,medium:108x5,medium:123x6,heavy:127x1</t>
+          <t>L20 W11/25; N=110; EHP=9953.250115; air:2x4,air:11x6,air:12x6,air:13x4,air:14x6,fast:30x3,fast:58x3,fast:64x4,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x1,medium:83x5,medium:108x5,medium:123x6,normal:17x14,normal:18x13,swarm:84x17 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>3882136,3882673,3882242,3882019,3882668,3882253,3882136,3882673,3882242,3882019,3882668,3882325,3882136,3882673,3882242,3882019,3882668,3882541,3882136,3882673,3882242,3882091,3882668,3882565,3882136,3882673,3882466,3882091,3882668,3882645,3882136,3882673,3882466,3882099,3882668,3882645,3882136,3882673,3882466,3882099,3882868,3882693,3882136,3882673,3882514,3882099,3882868,3882693,3882136,3882673,3882514,3882107,3882868,3882709,3882136,3882673,3882514,3882107,3882868,3882709,3882136,3882673,3882786,3882107,3882868,3883021,3882136,3882673,3882786,3882115,3882868,3882136,3882673,3882786,3882115,3882988,3882136,3882673,3882115,3882988,3882144,3882673,3882988,3882144,3882673,3882988,3882144,3882673,3882988,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882673,3882673,3882673</t>
+          <t>3882136,3882019,3882242,3882019,3882668,3882253,3882136,3882019,3882242,3882019,3882668,3882325,3882136,3882019,3882242,3882019,3882668,3882541,3882136,3882091,3882242,3882091,3882668,3882565,3882136,3882091,3882466,3882091,3882668,3882645,3882136,3882099,3882466,3882099,3882668,3882645,3882136,3882099,3882466,3882099,3882868,3882693,3882136,3882099,3882514,3882099,3882868,3882693,3882136,3882107,3882514,3882107,3882868,3882709,3882136,3882107,3882514,3882107,3882868,3882709,3882136,3882107,3882786,3882107,3882868,3883021,3882136,3882115,3882786,3882115,3882868,3882136,3882115,3882786,3882115,3882988,3882136,3882115,3882115,3882988,3882144,3882673,3882988,3882144,3882673,3882988,3882144,3882673,3882988,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882144,3882673,3882673,3882673,3882673</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>L20 W12/25; N=116; EHP=3936.000000; air:2x3,air:11x2,air:12x3,air:13x3,air:14x3,normal:17x14,normal:18x15,fast:30x4,heavy:31x1,heavy:40x1,fast:58x3,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x32,heavy:86x2,heavy:88x2,fast:98x3,medium:108x6,medium:123x5,heavy:127x1</t>
+          <t>L20 W12/25; N=116; EHP=10304.581974; air:2x6,air:11x4,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x3,fast:64x3,fast:98x3,heavy:31x1,heavy:40x1,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x6,medium:108x6,medium:123x5,normal:17x14,normal:18x15,swarm:84x18 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>3884136,3884673,3884242,3884019,3884668,3884253,3884136,3884673,3884242,3884019,3884668,3884253,3884136,3884673,3884242,3884019,3884668,3884325,3884136,3884673,3884466,3884091,3884668,3884325,3884136,3884673,3884466,3884091,3884668,3884541,3884136,3884673,3884466,3884091,3884668,3884565,3884136,3884673,3884466,3884099,3884868,3884645,3884136,3884673,3884514,3884099,3884868,3884645,3884136,3884673,3884514,3884099,3884868,3884693,3884136,3884673,3884514,3884107,3884868,3884693,3884136,3884673,3884786,3884107,3884868,3884709,3884136,3884673,3884786,3884107,3884868,3885021,3884136,3884673,3884786,3884115,3884988,3884136,3884673,3884786,3884115,3884988,3884136,3884673,3884115,3884988,3884144,3884673,3884988,3884144,3884673,3884988,3884144,3884673,3884988,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884673,3884673,3884673,3884673,3884673</t>
+          <t>3884136,3884019,3884242,3884019,3884668,3884253,3884136,3884019,3884242,3884019,3884668,3884253,3884136,3884019,3884242,3884019,3884668,3884325,3884136,3884091,3884466,3884091,3884668,3884325,3884136,3884091,3884466,3884091,3884668,3884541,3884136,3884091,3884466,3884091,3884668,3884565,3884136,3884099,3884466,3884099,3884868,3884645,3884136,3884099,3884514,3884099,3884868,3884645,3884136,3884099,3884514,3884099,3884868,3884693,3884136,3884107,3884514,3884107,3884868,3884693,3884136,3884107,3884786,3884107,3884868,3884709,3884136,3884107,3884786,3884107,3884868,3885021,3884136,3884115,3884786,3884115,3884988,3884136,3884115,3884786,3884115,3884988,3884136,3884115,3884115,3884988,3884144,3884673,3884988,3884144,3884673,3884988,3884144,3884673,3884988,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884144,3884673,3884673,3884673,3884673,3884673,3884673</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>L20 W13/25; N=122; EHP=4801.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x15,normal:18x14,fast:30x3,heavy:31x2,heavy:40x2,fast:58x4,fast:64x3,heavy:67x1,heavy:70x1,heavy:80x2,medium:83x6,swarm:84x34,heavy:86x2,heavy:88x1,fast:98x4,medium:108x6,medium:123x6,heavy:127x1</t>
+          <t>L20 W13/25; N=122; EHP=12571.565783; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x3,fast:58x4,fast:64x3,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x1,heavy:127x1,medium:83x6,medium:108x6,medium:123x6,normal:17x15,normal:18x14,swarm:84x19 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>3886136,3886673,3886242,3886019,3886668,3886253,3886136,3886673,3886242,3886019,3886668,3886253,3886136,3886673,3886242,3886019,3886668,3886325,3886136,3886673,3886242,3886091,3886668,3886325,3886136,3886673,3886466,3886091,3886668,3886541,3886136,3886673,3886466,3886091,3886668,3886565,3886136,3886673,3886466,3886099,3886868,3886645,3886136,3886673,3886466,3886099,3886868,3886693,3886136,3886673,3886514,3886099,3886868,3886693,3886136,3886673,3886514,3886107,3886868,3886709,3886136,3886673,3886514,3886107,3886868,3887021,3886136,3886673,3886514,3886107,3886868,3887021,3886136,3886673,3886786,3886115,3886988,3886136,3886673,3886786,3886115,3886988,3886136,3886673,3886786,3886115,3886988,3886136,3886673,3886988,3886144,3886673,3886988,3886144,3886673,3886988,3886144,3886673,3886988,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886673,3886673,3886673</t>
+          <t>3886136,3886019,3886242,3886019,3886668,3886253,3886136,3886019,3886242,3886019,3886668,3886253,3886136,3886019,3886242,3886019,3886668,3886325,3886136,3886091,3886242,3886091,3886668,3886325,3886136,3886091,3886466,3886091,3886668,3886541,3886136,3886091,3886466,3886091,3886668,3886565,3886136,3886099,3886466,3886099,3886868,3886645,3886136,3886099,3886466,3886099,3886868,3886693,3886136,3886099,3886514,3886099,3886868,3886693,3886136,3886107,3886514,3886107,3886868,3886709,3886136,3886107,3886514,3886107,3886868,3887021,3886136,3886107,3886514,3886107,3886868,3887021,3886136,3886115,3886786,3886115,3886988,3886136,3886115,3886786,3886115,3886988,3886136,3886115,3886786,3886115,3886988,3886136,3886673,3886988,3886144,3886673,3886988,3886144,3886673,3886988,3886144,3886673,3886988,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886144,3886673,3886673,3886673,3886673</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>L20 W14/25; N=128; EHP=5791.000000; air:2x3,air:11x3,air:12x3,air:13x3,air:14x3,normal:17x16,normal:18x16,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,heavy:67x1,heavy:70x1,heavy:80x1,medium:83x6,swarm:84x35,heavy:86x2,heavy:88x1,fast:98x3,medium:108x6,medium:123x7,heavy:127x2</t>
+          <t>L20 W14/25; N=128; EHP=15155.640335; air:2x6,air:11x6,air:12x6,air:13x6,air:14x6,fast:30x4,fast:58x4,fast:64x4,fast:98x3,heavy:31x2,heavy:40x2,heavy:67x1,heavy:70x1,heavy:80x1,heavy:86x2,heavy:88x1,heavy:127x2,medium:83x6,medium:108x6,medium:123x7,normal:17x16,normal:18x16,swarm:84x20 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>3888136,3888673,3888242,3888019,3888668,3888253,3888542,3888136,3888673,3888242,3888019,3888668,3888253,3888136,3888673,3888242,3888019,3888668,3888325,3888136,3888673,3888242,3888091,3888668,3888325,3888136,3888673,3888466,3888091,3888668,3888541,3888136,3888673,3888466,3888091,3888668,3888541,3888136,3888673,3888466,3888099,3888668,3888565,3888136,3888673,3888466,3888099,3888868,3888565,3888136,3888673,3888514,3888099,3888868,3888645,3888136,3888673,3888514,3888107,3888868,3888693,3888136,3888673,3888514,3888107,3888868,3888709,3888136,3888673,3888514,3888107,3888868,3889021,3888136,3888673,3888786,3888107,3888868,3889021,3888136,3888673,3888786,3888115,3888868,3888136,3888673,3888786,3888115,3888988,3888136,3888673,3888786,3888115,3888988,3888144,3888673,3888988,3888144,3888673,3888988,3888144,3888673,3888988,3888144,3888673,3888988,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888673,3888673,3888673,3888673,3888673,3888673</t>
+          <t>3888136,3888019,3888242,3888019,3888668,3888253,3888542,3888136,3888019,3888242,3888019,3888668,3888253,3888136,3888019,3888242,3888019,3888668,3888325,3888136,3888091,3888242,3888091,3888668,3888325,3888136,3888091,3888466,3888091,3888668,3888541,3888136,3888091,3888466,3888091,3888668,3888541,3888136,3888099,3888466,3888099,3888668,3888565,3888136,3888099,3888466,3888099,3888868,3888565,3888136,3888099,3888514,3888099,3888868,3888645,3888136,3888107,3888514,3888107,3888868,3888693,3888136,3888107,3888514,3888107,3888868,3888709,3888136,3888107,3888514,3888107,3888868,3889021,3888136,3888107,3888786,3888107,3888868,3889021,3888136,3888115,3888786,3888115,3888868,3888136,3888115,3888786,3888115,3888988,3888136,3888115,3888786,3888115,3888988,3888144,3888673,3888988,3888144,3888673,3888988,3888144,3888673,3888988,3888144,3888673,3888988,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888144,3888673,3888673,3888673,3888673,3888673,3888673,3888673</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>L20 W15/25; N=134; EHP=10107.000000; air:2x3,air:11x3,air:12x3,air:13x4,air:14x3,normal:17x16,normal:18x15,fast:30x4,heavy:31x2,heavy:40x2,fast:58x4,fast:64x4,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x1,medium:83x7,swarm:84x37,heavy:86x1,heavy:88x1,fast:98x4,medium:108x7,medium:123x6,heavy:127x2</t>
+          <t>L20 W15/25; N=134; EHP=26448.094932; air:2x6,air:11x6,air:12x6,air:13x8,air:14x6,elite:67x1,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x1,heavy:86x1,heavy:88x1,heavy:127x2,medium:83x7,medium:108x7,medium:123x6,normal:17x16,normal:18x15,swarm:84x21 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>3890136,3890673,3890242,3890019,3890668,3890253,3890136,3890673,3890242,3890019,3890668,3890325,3890136,3890673,3890242,3890019,3890668,3890325,3890136,3890673,3890242,3890091,3890668,3890541,3890136,3890673,3890466,3890091,3890668,3890541,3890136,3890673,3890466,3890091,3890668,3890565,3890136,3890673,3890466,3890091,3890668,3890565,3890136,3890673,3890466,3890099,3890868,3890645,3890136,3890673,3890514,3890099,3890868,3890645,3890136,3890673,3890514,3890099,3890868,3890693,3890136,3890673,3890514,3890107,3890868,3890709,3890136,3890673,3890514,3890107,3890868,3890709,3890136,3890673,3890786,3890107,3890868,3891021,3890136,3890673,3890786,3890115,3890868,3891021,3890136,3890673,3890786,3890115,3890988,3890136,3890673,3890786,3890115,3890988,3890144,3890673,3890115,3890988,3890144,3890673,3890988,3890144,3890673,3890988,3890144,3890673,3890988,3890144,3890673,3890988,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890673,3890673,3890673,3890673,3890673,3890673</t>
+          <t>3890136,3890019,3890242,3890019,3890668,3890253,3890136,3890019,3890242,3890019,3890668,3890325,3890136,3890019,3890242,3890019,3890668,3890325,3890136,3890091,3890242,3890091,3890668,3890541,3890136,3890091,3890466,3890091,3890668,3890541,3890136,3890091,3890466,3890091,3890668,3890565,3890136,3890091,3890466,3890091,3890668,3890565,3890136,3890099,3890466,3890099,3890868,3890645,3890136,3890099,3890514,3890099,3890868,3890645,3890136,3890099,3890514,3890099,3890868,3890693,3890136,3890107,3890514,3890107,3890868,3890709,3890136,3890107,3890514,3890107,3890868,3890709,3890136,3890107,3890786,3890107,3890868,3891021,3890136,3890115,3890786,3890115,3890868,3891021,3890136,3890115,3890786,3890115,3890988,3890136,3890115,3890786,3890115,3890988,3890144,3890115,3890115,3890988,3890144,3890673,3890988,3890144,3890673,3890988,3890144,3890673,3890988,3890144,3890673,3890988,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890144,3890673,3890673,3890673,3890673,3890673,3890673,3890673</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
-          <t>L20 W16/25; N=140; EHP=10310.000000; air:2x3,air:11x4,air:12x3,air:13x3,air:14x4,normal:17x16,normal:18x17,fast:30x4,heavy:31x1,heavy:40x2,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x39,heavy:86x1,heavy:88x2,fast:98x4,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L20 W16/25; N=140; EHP=26991.756283; air:2x6,air:11x8,air:12x6,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x4,fast:98x4,heavy:31x1,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x1,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x16,normal:18x17,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>3892136,3892673,3892242,3892019,3892668,3892253,3892136,3892673,3892242,3892019,3892668,3892325,3892136,3892673,3892242,3892019,3892668,3892541,3892136,3892673,3892242,3892019,3892668,3892541,3892136,3892673,3892466,3892091,3892668,3892565,3892136,3892673,3892466,3892091,3892668,3892565,3892136,3892673,3892466,3892091,3892668,3892645,3892136,3892673,3892466,3892099,3892868,3892645,3892136,3892673,3892514,3892099,3892868,3892693,3892136,3892673,3892514,3892099,3892868,3892693,3892136,3892673,3892514,3892099,3892868,3892709,3892136,3892673,3892514,3892107,3892868,3892709,3892136,3892673,3892786,3892107,3892868,3893021,3892136,3892673,3892786,3892107,3892868,3893021,3892136,3892673,3892786,3892115,3892988,3892136,3892673,3892786,3892115,3892988,3892136,3892673,3892786,3892115,3892988,3892136,3892673,3892115,3892988,3892144,3892673,3892988,3892144,3892673,3892988,3892144,3892673,3892988,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892673,3892673,3892673,3892673</t>
+          <t>3892136,3892019,3892242,3892019,3892668,3892253,3892136,3892019,3892242,3892019,3892668,3892325,3892136,3892019,3892242,3892019,3892668,3892541,3892136,3892019,3892242,3892019,3892668,3892541,3892136,3892091,3892466,3892091,3892668,3892565,3892136,3892091,3892466,3892091,3892668,3892565,3892136,3892091,3892466,3892091,3892668,3892645,3892136,3892099,3892466,3892099,3892868,3892645,3892136,3892099,3892514,3892099,3892868,3892693,3892136,3892099,3892514,3892099,3892868,3892693,3892136,3892099,3892514,3892099,3892868,3892709,3892136,3892107,3892514,3892107,3892868,3892709,3892136,3892107,3892786,3892107,3892868,3893021,3892136,3892107,3892786,3892107,3892868,3893021,3892136,3892115,3892786,3892115,3892988,3892136,3892115,3892786,3892115,3892988,3892136,3892115,3892786,3892115,3892988,3892136,3892115,3892115,3892988,3892144,3892673,3892988,3892144,3892673,3892988,3892144,3892673,3892988,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892144,3892673,3892673,3892673,3892673,3892673</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
-          <t>L20 W17/25; N=146; EHP=10517.000000; air:2x4,air:11x3,air:12x4,air:13x3,air:14x4,normal:17x18,normal:18x18,fast:30x4,heavy:31x1,heavy:40x1,fast:58x4,fast:64x4,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x40,heavy:86x2,heavy:88x2,fast:98x5,medium:108x7,medium:123x7,heavy:127x2</t>
+          <t>L20 W17/25; N=146; EHP=27541.326124; air:2x8,air:11x6,air:12x8,air:13x6,air:14x8,fast:30x4,fast:58x4,fast:64x4,fast:98x5,heavy:31x1,heavy:40x1,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x7,medium:108x7,medium:123x7,normal:17x18,normal:18x18,swarm:84x22 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>3894136,3894673,3894242,3894019,3894668,3894253,3894136,3894673,3894242,3894019,3894668,3894253,3894136,3894673,3894242,3894019,3894668,3894325,3894136,3894673,3894242,3894019,3894668,3894325,3894136,3894673,3894466,3894091,3894668,3894541,3894136,3894673,3894466,3894091,3894668,3894541,3894136,3894673,3894466,3894091,3894668,3894565,3894136,3894673,3894466,3894099,3894868,3894565,3894136,3894673,3894466,3894099,3894868,3894645,3894136,3894673,3894514,3894099,3894868,3894645,3894136,3894673,3894514,3894099,3894868,3894693,3894136,3894673,3894514,3894107,3894868,3894693,3894136,3894673,3894514,3894107,3894868,3894709,3894136,3894673,3894514,3894107,3894868,3894709,3894136,3894673,3894786,3894107,3894868,3895021,3894136,3894673,3894786,3894115,3894988,3894136,3894673,3894786,3894115,3894988,3894136,3894673,3894786,3894115,3894988,3894144,3894673,3894988,3894144,3894673,3894988,3894144,3894673,3894988,3894144,3894673,3894988,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894673,3894673,3894673,3894673,3894673</t>
+          <t>3894136,3894019,3894242,3894019,3894668,3894253,3894136,3894019,3894242,3894019,3894668,3894253,3894136,3894019,3894242,3894019,3894668,3894325,3894136,3894019,3894242,3894019,3894668,3894325,3894136,3894091,3894466,3894091,3894668,3894541,3894136,3894091,3894466,3894091,3894668,3894541,3894136,3894091,3894466,3894091,3894668,3894565,3894136,3894099,3894466,3894099,3894868,3894565,3894136,3894099,3894466,3894099,3894868,3894645,3894136,3894099,3894514,3894099,3894868,3894645,3894136,3894099,3894514,3894099,3894868,3894693,3894136,3894107,3894514,3894107,3894868,3894693,3894136,3894107,3894514,3894107,3894868,3894709,3894136,3894107,3894514,3894107,3894868,3894709,3894136,3894107,3894786,3894107,3894868,3895021,3894136,3894115,3894786,3894115,3894988,3894136,3894115,3894786,3894115,3894988,3894136,3894115,3894786,3894115,3894988,3894144,3894673,3894988,3894144,3894673,3894988,3894144,3894673,3894988,3894144,3894673,3894988,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894144,3894673,3894673,3894673,3894673,3894673,3894673</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
-          <t>L20 W18/25; N=152; EHP=11235.000000; air:2x4,air:11x3,air:12x4,air:13x4,air:14x3,normal:17x18,normal:18x19,fast:30x4,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x7,swarm:84x42,heavy:86x2,heavy:88x2,fast:98x4,medium:108x8,medium:123x7,heavy:127x1</t>
+          <t>L20 W18/25; N=152; EHP=29406.133941; air:2x8,air:11x6,air:12x8,air:13x8,air:14x6,fast:30x4,fast:58x5,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x1,medium:83x7,medium:108x8,medium:123x7,normal:17x18,normal:18x19,swarm:84x24 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>3896136,3896673,3896242,3896019,3896668,3896253,3896136,3896673,3896242,3896019,3896668,3896253,3896136,3896673,3896242,3896019,3896668,3896325,3896136,3896673,3896242,3896019,3896668,3896325,3896136,3896673,3896242,3896091,3896668,3896541,3896136,3896673,3896466,3896091,3896668,3896541,3896136,3896673,3896466,3896091,3896668,3896565,3896136,3896673,3896466,3896091,3896668,3896645,3896136,3896673,3896466,3896099,3896868,3896645,3896136,3896673,3896514,3896099,3896868,3896693,3896136,3896673,3896514,3896099,3896868,3896693,3896136,3896673,3896514,3896107,3896868,3896709,3896136,3896673,3896514,3896107,3896868,3896709,3896136,3896673,3896514,3896107,3896868,3897021,3896136,3896673,3896786,3896107,3896868,3897021,3896136,3896673,3896786,3896115,3896988,3896136,3896673,3896786,3896115,3896988,3896136,3896673,3896786,3896115,3896988,3896136,3896673,3896115,3896988,3896136,3896673,3896988,3896144,3896673,3896988,3896144,3896673,3896988,3896144,3896673,3896988,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896673,3896673,3896673,3896673,3896673</t>
+          <t>3896136,3896019,3896242,3896019,3896668,3896253,3896136,3896019,3896242,3896019,3896668,3896253,3896136,3896019,3896242,3896019,3896668,3896325,3896136,3896019,3896242,3896019,3896668,3896325,3896136,3896091,3896242,3896091,3896668,3896541,3896136,3896091,3896466,3896091,3896668,3896541,3896136,3896091,3896466,3896091,3896668,3896565,3896136,3896091,3896466,3896091,3896668,3896645,3896136,3896099,3896466,3896099,3896868,3896645,3896136,3896099,3896514,3896099,3896868,3896693,3896136,3896099,3896514,3896099,3896868,3896693,3896136,3896107,3896514,3896107,3896868,3896709,3896136,3896107,3896514,3896107,3896868,3896709,3896136,3896107,3896514,3896107,3896868,3897021,3896136,3896107,3896786,3896107,3896868,3897021,3896136,3896115,3896786,3896115,3896988,3896136,3896115,3896786,3896115,3896988,3896136,3896115,3896786,3896115,3896988,3896136,3896115,3896115,3896988,3896136,3896673,3896988,3896144,3896673,3896988,3896144,3896673,3896988,3896144,3896673,3896988,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896144,3896673,3896673,3896673,3896673,3896673,3896673</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
-          <t>L20 W19/25; N=158; EHP=13014.000000; air:2x4,air:11x4,air:12x3,air:13x4,air:14x4,normal:17x20,normal:18x19,fast:30x5,heavy:31x2,heavy:40x2,fast:58x4,fast:64x5,heavy:67x2,heavy:70x1,heavy:80x2,medium:83x8,swarm:84x44,heavy:86x2,heavy:88x2,fast:98x4,medium:108x7,medium:123x8,heavy:127x2</t>
+          <t>L20 W19/25; N=158; EHP=34070.247299; air:2x8,air:11x8,air:12x6,air:13x8,air:14x8,fast:30x5,fast:58x4,fast:64x5,fast:98x4,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x1,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x7,medium:123x8,normal:17x20,normal:18x19,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>3898136,3898673,3898242,3898019,3898668,3898253,3898542,3898136,3898673,3898242,3898019,3898668,3898253,3898136,3898673,3898242,3898019,3898668,3898325,3898136,3898673,3898242,3898019,3898668,3898325,3898136,3898673,3898242,3898091,3898668,3898541,3898136,3898673,3898466,3898091,3898668,3898541,3898136,3898673,3898466,3898091,3898668,3898565,3898136,3898673,3898466,3898091,3898668,3898565,3898136,3898673,3898466,3898099,3898868,3898645,3898136,3898673,3898466,3898099,3898868,3898645,3898136,3898673,3898514,3898099,3898868,3898693,3898136,3898673,3898514,3898099,3898868,3898693,3898136,3898673,3898514,3898107,3898868,3898709,3898136,3898673,3898514,3898107,3898868,3898709,3898136,3898673,3898786,3898107,3898868,3899021,3898136,3898673,3898786,3898107,3898868,3899021,3898136,3898673,3898786,3898115,3898988,3898136,3898673,3898786,3898115,3898988,3898136,3898673,3898786,3898115,3898988,3898144,3898673,3898115,3898988,3898144,3898673,3898988,3898144,3898673,3898988,3898144,3898673,3898988,3898144,3898673,3898988,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898673,3898673,3898673,3898673,3898673,3898673</t>
+          <t>3898136,3898019,3898242,3898019,3898668,3898253,3898542,3898136,3898019,3898242,3898019,3898668,3898253,3898136,3898019,3898242,3898019,3898668,3898325,3898136,3898019,3898242,3898019,3898668,3898325,3898136,3898091,3898242,3898091,3898668,3898541,3898136,3898091,3898466,3898091,3898668,3898541,3898136,3898091,3898466,3898091,3898668,3898565,3898136,3898091,3898466,3898091,3898668,3898565,3898136,3898099,3898466,3898099,3898868,3898645,3898136,3898099,3898466,3898099,3898868,3898645,3898136,3898099,3898514,3898099,3898868,3898693,3898136,3898099,3898514,3898099,3898868,3898693,3898136,3898107,3898514,3898107,3898868,3898709,3898136,3898107,3898514,3898107,3898868,3898709,3898136,3898107,3898786,3898107,3898868,3899021,3898136,3898107,3898786,3898107,3898868,3899021,3898136,3898115,3898786,3898115,3898988,3898136,3898115,3898786,3898115,3898988,3898136,3898115,3898786,3898115,3898988,3898144,3898115,3898115,3898988,3898144,3898673,3898988,3898144,3898673,3898988,3898144,3898673,3898988,3898144,3898673,3898988,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898144,3898673,3898673,3898673,3898673,3898673,3898673,3898673</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
-          <t>L20 W20/25; N=164; EHP=21846.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x19,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x4,elite:67x1,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x8,swarm:84x45,heavy:86x2,heavy:88x2,fast:98x5,medium:108x8,medium:123x8,heavy:127x2</t>
+          <t>L20 W20/25; N=164; EHP=57184.449313; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,elite:67x1,fast:30x5,fast:58x5,fast:64x4,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x8,medium:123x8,normal:17x19,normal:18x20,swarm:84x25 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>10018421,10018432,10018423,10048660,10018431,10018424,10018421,10018432,10018423,10048660,10018431,10018424,10018421,10018432,10018423,10048660,10018431,10018425,10018421,10018432,10018423,10048660,10018431,10018425,10018421,10018432,10018423,10018418,10018431,10018428,10018421,10018432,10018426,10018418,10018431,10018428,10018421,10018432,10018426,10018418,10018431,10018429,10018421,10018432,10018426,10018418,10018431,10018429,10018421,10018432,10018426,10048661,10018435,10018430,10018421,10018432,10018426,10048661,10018435,10018430,10018421,10018432,10018427,10048661,10018435,10018430,10018421,10018432,10018427,10048661,10018435,10018433,10018421,10018432,10018427,10018419,10018435,10018433,10018421,10018432,10018427,10018419,10018435,10045202,10018421,10018432,10018427,10018419,10018435,10045202,10018421,10018432,10018434,10018419,10018435,10018437,10018421,10018432,10018434,10018420,10018435,10018437,10018421,10018432,10018434,10018420,10018436,10018421,10018432,10018434,10018420,10018436,10018421,10018432,10018434,10018420,10018436,10018421,10018432,10018436,10018422,10018432,10018436,10018422,10018432,10018436,10018422,10018432,10018436,10018422,10018432,10018436,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018432,10018432,10018432,10018432,10018432,10018432</t>
+          <t>10018421,10048660,10018423,10048660,10018431,10018424,10018421,10048660,10018423,10048660,10018431,10018424,10018421,10048660,10018423,10048660,10018431,10018425,10018421,10048660,10018423,10048660,10018431,10018425,10018421,10018418,10018423,10018418,10018431,10018428,10018421,10018418,10018426,10018418,10018431,10018428,10018421,10018418,10018426,10018418,10018431,10018429,10018421,10018418,10018426,10018418,10018431,10018429,10018421,10048661,10018426,10048661,10018435,10018430,10018421,10048661,10018426,10048661,10018435,10018430,10018421,10048661,10018427,10048661,10018435,10018430,10018421,10048661,10018427,10048661,10018435,10018433,10018421,10018419,10018427,10018419,10018435,10018433,10018421,10018419,10018427,10018419,10018435,10045202,10018421,10018419,10018427,10018419,10018435,10045202,10018421,10018419,10018434,10018419,10018435,10018437,10018421,10018420,10018434,10018420,10018435,10018437,10018421,10018420,10018434,10018420,10018436,10018421,10018420,10018434,10018420,10018436,10018421,10018420,10018434,10018420,10018436,10018421,10018432,10018436,10018422,10018432,10018436,10018422,10018432,10018436,10018422,10018432,10018436,10018422,10018432,10018436,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018422,10018432,10018432,10018432,10018432,10018432,10018432,10018432</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>L20 W21/25; N=170; EHP=22283.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x4,normal:17x21,normal:18x20,fast:30x5,heavy:31x2,heavy:40x2,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x3,medium:83x8,swarm:84x47,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x8,heavy:127x2</t>
+          <t>L20 W21/25; N=170; EHP=58316.221888; air:2x8,air:11x8,air:12x8,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x3,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x8,medium:108x9,medium:123x8,normal:17x21,normal:18x20,swarm:84x27 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>10018441,10018451,10018443,10048662,10018450,10018444,10018441,10018451,10018443,10048662,10018450,10018444,10018441,10018451,10018443,10048662,10018450,10018445,10018441,10018451,10018443,10048662,10018450,10018445,10018441,10018451,10018443,10018438,10018450,10018448,10018441,10018451,10018446,10018438,10018450,10018448,10018441,10018451,10018446,10018438,10018450,10018449,10018441,10018451,10018446,10018438,10018450,10018449,10018441,10018451,10018446,10048663,10018450,10045203,10018441,10018451,10018446,10048663,10018455,10045203,10018441,10018451,10018446,10048663,10018455,10018452,10018441,10018451,10018447,10048663,10018455,10018452,10018441,10018451,10018447,10018439,10018455,10018452,10018441,10018451,10018447,10018439,10018455,10018453,10018441,10018451,10018447,10018439,10018455,10018453,10018441,10018451,10018447,10018439,10018455,10018457,10018441,10018451,10018454,10018440,10018455,10018457,10018441,10018451,10018454,10018440,10018456,10018441,10018451,10018454,10018440,10018456,10018441,10018451,10018454,10018440,10018456,10018441,10018451,10018454,10018440,10018456,10018442,10018451,10018456,10018442,10018451,10018456,10018442,10018451,10018456,10018442,10018451,10018456,10018442,10018451,10018456,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018451,10018451,10018451,10018451,10018451,10018451,10018451</t>
+          <t>10018441,10048662,10018443,10048662,10018450,10018444,10018441,10048662,10018443,10048662,10018450,10018444,10018441,10048662,10018443,10048662,10018450,10018445,10018441,10048662,10018443,10048662,10018450,10018445,10018441,10018438,10018443,10018438,10018450,10018448,10018441,10018438,10018446,10018438,10018450,10018448,10018441,10018438,10018446,10018438,10018450,10018449,10018441,10018438,10018446,10018438,10018450,10018449,10018441,10048663,10018446,10048663,10018450,10045203,10018441,10048663,10018446,10048663,10018455,10045203,10018441,10048663,10018446,10048663,10018455,10018452,10018441,10048663,10018447,10048663,10018455,10018452,10018441,10018439,10018447,10018439,10018455,10018452,10018441,10018439,10018447,10018439,10018455,10018453,10018441,10018439,10018447,10018439,10018455,10018453,10018441,10018439,10018447,10018439,10018455,10018457,10018441,10018440,10018454,10018440,10018455,10018457,10018441,10018440,10018454,10018440,10018456,10018441,10018440,10018454,10018440,10018456,10018441,10018440,10018454,10018440,10018456,10018441,10018440,10018454,10018440,10018456,10018442,10018451,10018456,10018442,10018451,10018456,10018442,10018451,10018456,10018442,10018451,10018456,10018442,10018451,10018456,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018442,10018451,10018451,10018451,10018451,10018451,10018451,10018451,10018451</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>L20 W22/25; N=176; EHP=22729.000000; air:2x4,air:11x4,air:12x4,air:13x4,air:14x5,normal:17x21,normal:18x21,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x49,heavy:86x3,heavy:88x2,fast:98x5,medium:108x8,medium:123x9,heavy:127x2</t>
+          <t>L20 W22/25; N=176; EHP=59496.395905; air:2x8,air:11x8,air:12x8,air:13x8,air:14x10,fast:30x5,fast:58x6,fast:64x5,fast:98x5,heavy:31x2,heavy:40x2,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x3,heavy:88x2,heavy:127x2,medium:83x9,medium:108x8,medium:123x9,normal:17x21,normal:18x21,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>10018461,10018472,10018463,10048664,10018471,10018464,10018461,10018472,10018463,10048664,10018471,10018464,10018461,10018472,10018463,10048664,10018471,10018464,10018461,10018472,10018463,10048664,10018471,10018465,10018461,10018472,10018463,10048664,10018471,10018465,10018461,10018472,10018466,10018458,10018471,10018465,10018461,10018472,10018466,10018458,10018471,10018468,10018461,10018472,10018466,10018458,10018471,10018468,10018461,10018472,10018466,10018458,10018471,10018469,10018461,10018472,10018466,10048665,10018476,10018469,10018461,10018472,10018467,10048665,10018476,10018470,10018461,10018472,10018467,10048665,10018476,10018470,10018461,10018472,10018467,10048665,10018476,10018473,10018461,10018472,10018467,10048665,10018476,10018473,10018461,10018472,10018467,10018459,10018476,10018474,10018461,10018472,10018467,10018459,10018476,10018474,10018461,10018472,10018475,10018459,10018476,10018478,10018461,10018472,10018475,10018459,10018476,10018478,10018461,10018472,10018475,10018460,10018477,10018461,10018472,10018475,10018460,10018477,10018461,10018472,10018475,10018460,10018477,10018461,10018472,10018460,10018477,10018462,10018472,10018477,10018462,10018472,10018477,10018462,10018472,10018477,10018462,10018472,10018477,10018462,10018472,10018477,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018472,10018472,10018472,10018472,10018472,10018472</t>
+          <t>10018461,10048664,10018463,10048664,10018471,10018464,10018461,10048664,10018463,10048664,10018471,10018464,10018461,10048664,10018463,10048664,10018471,10018464,10018461,10048664,10018463,10048664,10018471,10018465,10018461,10048664,10018463,10048664,10018471,10018465,10018461,10018458,10018466,10018458,10018471,10018465,10018461,10018458,10018466,10018458,10018471,10018468,10018461,10018458,10018466,10018458,10018471,10018468,10018461,10018458,10018466,10018458,10018471,10018469,10018461,10048665,10018466,10048665,10018476,10018469,10018461,10048665,10018467,10048665,10018476,10018470,10018461,10048665,10018467,10048665,10018476,10018470,10018461,10048665,10018467,10048665,10018476,10018473,10018461,10048665,10018467,10048665,10018476,10018473,10018461,10018459,10018467,10018459,10018476,10018474,10018461,10018459,10018467,10018459,10018476,10018474,10018461,10018459,10018475,10018459,10018476,10018478,10018461,10018459,10018475,10018459,10018476,10018478,10018461,10018460,10018475,10018460,10018477,10018461,10018460,10018475,10018460,10018477,10018461,10018460,10018475,10018460,10018477,10018461,10018460,10018460,10018477,10018462,10018472,10018477,10018462,10018472,10018477,10018462,10018472,10018477,10018462,10018472,10018477,10018462,10018472,10018477,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018462,10018472,10018472,10018472,10018472,10018472,10018472,10018472</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>L20 W23/25; N=182; EHP=23184.000000; air:2x5,air:11x4,air:12x5,air:13x4,air:14x4,normal:17x22,normal:18x22,fast:30x5,heavy:31x3,heavy:40x3,fast:58x5,fast:64x6,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x50,heavy:86x2,heavy:88x2,fast:98x5,medium:108x9,medium:123x9,heavy:127x2</t>
+          <t>L20 W23/25; N=182; EHP=60693.608714; air:2x10,air:11x8,air:12x10,air:13x8,air:14x8,fast:30x5,fast:58x5,fast:64x6,fast:98x5,heavy:31x3,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x2,medium:83x9,medium:108x9,medium:123x9,normal:17x22,normal:18x22,swarm:84x28 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>10018482,10018493,10018484,10048666,10018492,10018485,10018482,10018493,10018484,10048666,10018492,10018485,10018482,10018493,10018484,10048666,10018492,10018486,10018482,10018493,10018484,10048666,10018492,10018486,10018482,10018493,10018484,10048666,10018492,10018486,10018482,10018493,10018484,10018479,10018492,10018489,10018482,10018493,10018487,10018479,10018492,10018489,10018482,10018493,10018487,10018479,10018492,10018490,10018482,10018493,10018487,10018479,10018492,10018490,10018482,10018493,10018487,10018479,10018497,10018491,10018482,10018493,10018487,10048667,10018497,10018491,10018482,10018493,10018488,10048667,10018497,10018494,10018482,10018493,10018488,10048667,10018497,10018494,10018482,10018493,10018488,10048667,10018497,10018495,10018482,10018493,10018488,10018480,10018497,10018495,10018482,10018493,10018488,10018480,10018497,10018499,10018482,10018493,10018496,10018480,10018497,10018499,10018482,10018493,10018496,10018480,10018497,10018499,10018482,10018493,10018496,10018480,10018497,10018482,10018493,10018496,10018481,10018498,10018482,10018493,10018496,10018481,10018498,10018482,10018493,10018496,10018481,10018498,10018483,10018493,10018481,10018498,10018483,10018493,10018498,10018483,10018493,10018498,10018483,10018493,10018498,10018483,10018493,10018498,10018483,10018493,10018498,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018493,10018493,10018493,10018493,10018493,10018493,10018493</t>
+          <t>10018482,10048666,10018484,10048666,10018492,10018485,10018482,10048666,10018484,10048666,10018492,10018485,10018482,10048666,10018484,10048666,10018492,10018486,10018482,10048666,10018484,10048666,10018492,10018486,10018482,10048666,10018484,10048666,10018492,10018486,10018482,10018479,10018484,10018479,10018492,10018489,10018482,10018479,10018487,10018479,10018492,10018489,10018482,10018479,10018487,10018479,10018492,10018490,10018482,10018479,10018487,10018479,10018492,10018490,10018482,10018479,10018487,10018479,10018497,10018491,10018482,10048667,10018487,10048667,10018497,10018491,10018482,10048667,10018488,10048667,10018497,10018494,10018482,10048667,10018488,10048667,10018497,10018494,10018482,10048667,10018488,10048667,10018497,10018495,10018482,10018480,10018488,10018480,10018497,10018495,10018482,10018480,10018488,10018480,10018497,10018499,10018482,10018480,10018496,10018480,10018497,10018499,10018482,10018480,10018496,10018480,10018497,10018499,10018482,10018480,10018496,10018480,10018497,10018482,10018481,10018496,10018481,10018498,10018482,10018481,10018496,10018481,10018498,10018482,10018481,10018496,10018481,10018498,10018483,10018481,10018481,10018498,10018483,10018493,10018498,10018483,10018493,10018498,10018483,10018493,10018498,10018483,10018493,10018498,10018483,10018493,10018498,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018483,10018493,10018493,10018493,10018493,10018493,10018493,10018493,10018493</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>L20 W24/25; N=188; EHP=24826.000000; air:2x5,air:11x5,air:12x4,air:13x5,air:14x4,normal:17x22,normal:18x23,fast:30x6,heavy:31x2,heavy:40x3,fast:58x5,fast:64x5,heavy:67x2,heavy:70x2,heavy:80x2,medium:83x9,swarm:84x52,heavy:86x2,heavy:88x2,fast:98x6,medium:108x10,medium:123x9,heavy:127x3</t>
+          <t>L20 W24/25; N=188; EHP=65004.913933; air:2x10,air:11x10,air:12x8,air:13x10,air:14x8,fast:30x6,fast:58x5,fast:64x5,fast:98x6,heavy:31x2,heavy:40x3,heavy:67x2,heavy:70x2,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x9,medium:108x10,medium:123x9,normal:17x22,normal:18x23,swarm:84x29 | manual: L1-scaled</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>10018503,10018514,10018505,10048668,10018513,10018506,10018521,10018503,10018514,10018505,10048668,10018513,10018506,10018503,10018514,10018505,10048668,10018513,10018507,10018503,10018514,10018505,10048668,10018513,10018507,10018503,10018514,10018505,10018500,10018513,10018510,10018503,10018514,10018508,10018500,10018513,10018510,10018503,10018514,10018508,10018500,10018513,10018510,10018503,10018514,10018508,10018500,10018513,10018511,10018503,10018514,10018508,10018500,10018513,10018511,10018503,10018514,10018508,10048669,10018513,10018511,10018503,10018514,10018508,10048669,10018518,10018512,10018503,10018514,10018509,10048669,10018518,10018512,10018503,10018514,10018509,10048669,10018518,10018515,10018503,10018514,10018509,10018501,10018518,10018515,10018503,10018514,10018509,10018501,10018518,10018516,10018503,10018514,10018509,10018501,10018518,10018516,10018503,10018514,10018509,10018501,10018518,10018520,10018503,10018514,10018517,10018501,10018518,10018520,10018503,10018514,10018517,10018502,10018518,10018520,10018503,10018514,10018517,10018502,10018519,10018503,10018514,10018517,10018502,10018519,10018503,10018514,10018517,10018502,10018519,10018503,10018514,10018517,10018502,10018519,10018504,10018514,10018519,10018504,10018514,10018519,10018504,10018514,10018519,10018504,10018514,10018519,10018504,10018514,10018519,10018504,10018514,10018519,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018514,10018514,10018514,10018514,10018514,10018514,10018514,10018514,10018514</t>
+          <t>10018503,10048668,10018505,10048668,10018513,10018506,10018521,10018503,10048668,10018505,10048668,10018513,10018506,10018503,10048668,10018505,10048668,10018513,10018507,10018503,10048668,10018505,10048668,10018513,10018507,10018503,10018500,10018505,10018500,10018513,10018510,10018503,10018500,10018508,10018500,10018513,10018510,10018503,10018500,10018508,10018500,10018513,10018510,10018503,10018500,10018508,10018500,10018513,10018511,10018503,10018500,10018508,10018500,10018513,10018511,10018503,10048669,10018508,10048669,10018513,10018511,10018503,10048669,10018508,10048669,10018518,10018512,10018503,10048669,10018509,10048669,10018518,10018512,10018503,10048669,10018509,10048669,10018518,10018515,10018503,10018501,10018509,10018501,10018518,10018515,10018503,10018501,10018509,10018501,10018518,10018516,10018503,10018501,10018509,10018501,10018518,10018516,10018503,10018501,10018509,10018501,10018518,10018520,10018503,10018501,10018517,10018501,10018518,10018520,10018503,10018502,10018517,10018502,10018518,10018520,10018503,10018502,10018517,10018502,10018519,10018503,10018502,10018517,10018502,10018519,10018503,10018502,10018517,10018502,10018519,10018503,10018502,10018517,10018502,10018519,10018504,10018514,10018519,10018504,10018514,10018519,10018504,10018514,10018519,10018504,10018514,10018519,10018504,10018514,10018519,10018504,10018514,10018519,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018504,10018514,10018514,10018514,10018514,10018514,10018514,10018514,10018514,10018514,10018514</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>L20 W25/25; N=194; EHP=49550.000000; air:2x4,air:11x5,air:12x4,air:13x5,air:14x5,normal:17x23,normal:18x22,fast:30x5,heavy:31x2,heavy:40x2,fast:58x6,fast:64x6,heavy:67x3,heavy:70x3,heavy:80x2,medium:83x10,swarm:84x54,heavy:86x2,heavy:88x2,fast:98x6,medium:108x9,medium:123x10,heavy:127x3,boss:132x1</t>
+          <t>L20 W25/25; N=194; EHP=129661.679337; air:2x8,air:11x10,air:12x8,air:13x10,air:14x10,boss:132x1,fast:30x5,fast:58x6,fast:64x6,fast:98x6,heavy:31x2,heavy:40x2,heavy:67x3,heavy:70x3,heavy:80x2,heavy:86x2,heavy:88x2,heavy:127x3,medium:83x10,medium:108x9,medium:123x10,normal:17x23,normal:18x22,swarm:84x31 | manual: L1-scaled</t>
         </is>
       </c>
     </row>

--- a/Luban/Config/Datas/Levels/L20/EnemyList.xlsx
+++ b/Luban/Config/Datas/Levels/L20/EnemyList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28125" windowHeight="12540" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="144525" fullCalcOnLoad="1"/>
@@ -1165,7 +1165,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="0" t="n">
-        <v>242</v>
+        <v>340</v>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>235</v>
+        <v>300</v>
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>221</v>
+        <v>360</v>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="0" t="n">
-        <v>214</v>
+        <v>290</v>
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>200</v>
+        <v>290</v>
       </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>193</v>
+        <v>270</v>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>186</v>
+        <v>360</v>
       </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0" t="n">
-        <v>179</v>
+        <v>280</v>
       </c>
       <c r="F13" s="0" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>172</v>
+        <v>205</v>
       </c>
       <c r="F14" s="0" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0" t="n">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="F15" s="0" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0" t="n">
-        <v>158</v>
+        <v>280</v>
       </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="0" t="n">
-        <v>151</v>
+        <v>260</v>
       </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="0" t="n">
-        <v>144</v>
+        <v>360</v>
       </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
@@ -1480,7 +1480,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="0" t="n">
-        <v>137</v>
+        <v>290</v>
       </c>
       <c r="F19" s="0" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="0" t="n">
-        <v>130</v>
+        <v>270</v>
       </c>
       <c r="F20" s="0" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="0" t="n">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="F21" s="0" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="0" t="n">
-        <v>128</v>
+        <v>300</v>
       </c>
       <c r="F22" s="0" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="0" t="n">
-        <v>128</v>
+        <v>260</v>
       </c>
       <c r="F23" s="0" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="0" t="n">
-        <v>128</v>
+        <v>290</v>
       </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="0" t="n">
-        <v>128</v>
+        <v>360</v>
       </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="0" t="n">
-        <v>128</v>
+        <v>270</v>
       </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="0" t="n">
-        <v>128</v>
+        <v>310</v>
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="0" t="n">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
